--- a/docentes/Gomez Lopez Javier - Estadisticos 20222.xlsx
+++ b/docentes/Gomez Lopez Javier - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="17">
   <si>
     <t>Mat</t>
   </si>
@@ -68,15 +68,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>BUSTOS</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>LUZ DEL CARMEN</t>
   </si>
 </sst>
 </file>
@@ -477,16 +468,19 @@
         <v>33</v>
       </c>
       <c r="D2">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>78.79000000000001</v>
+      </c>
+      <c r="H2">
+        <v>7.2</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -500,16 +494,19 @@
         <v>29</v>
       </c>
       <c r="D3">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>82.76000000000001</v>
+      </c>
+      <c r="H3">
+        <v>7.1</v>
       </c>
     </row>
   </sheetData>
@@ -565,7 +562,7 @@
         <v>33</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -588,7 +585,7 @@
         <v>29</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -647,16 +644,19 @@
         <v>33</v>
       </c>
       <c r="D2">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>78.79000000000001</v>
+      </c>
+      <c r="H2">
+        <v>7.2</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -670,16 +670,19 @@
         <v>29</v>
       </c>
       <c r="D3">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>82.76000000000001</v>
+      </c>
+      <c r="H3">
+        <v>7.1</v>
       </c>
     </row>
   </sheetData>
@@ -689,7 +692,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -719,29 +722,6 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>19330051920361</v>
-      </c>
-      <c r="B2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Gomez Lopez Javier - Estadisticos 20222.xlsx
+++ b/docentes/Gomez Lopez Javier - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="26">
   <si>
     <t>Mat</t>
   </si>
@@ -68,6 +68,33 @@
   </si>
   <si>
     <t>Reprobadas</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>TENTZOHUA</t>
+  </si>
+  <si>
+    <t>COMIHUA</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
+    <t>LEÓN</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>MARIA TERESA</t>
+  </si>
+  <si>
+    <t>RUBI</t>
+  </si>
+  <si>
+    <t>ALEJANDRO GABRIEL</t>
   </si>
 </sst>
 </file>
@@ -692,7 +719,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -722,6 +749,75 @@
         <v>16</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>21330051920260</v>
+      </c>
+      <c r="B2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>21330051920107</v>
+      </c>
+      <c r="B3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>21330051920036</v>
+      </c>
+      <c r="B4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Gomez Lopez Javier - Estadisticos 20222.xlsx
+++ b/docentes/Gomez Lopez Javier - Estadisticos 20222.xlsx
@@ -492,22 +492,22 @@
         <v>9</v>
       </c>
       <c r="C2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D2">
         <v>1</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F2">
         <v>26</v>
       </c>
       <c r="G2">
-        <v>78.79000000000001</v>
+        <v>76.47</v>
       </c>
       <c r="H2">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -518,10 +518,10 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3">
         <v>5</v>
@@ -530,7 +530,7 @@
         <v>24</v>
       </c>
       <c r="G3">
-        <v>82.76000000000001</v>
+        <v>80</v>
       </c>
       <c r="H3">
         <v>7.1</v>
@@ -583,13 +583,13 @@
         <v>9</v>
       </c>
       <c r="C2">
+        <v>34</v>
+      </c>
+      <c r="D2">
+        <v>34</v>
+      </c>
+      <c r="E2">
         <v>33</v>
-      </c>
-      <c r="D2">
-        <v>33</v>
-      </c>
-      <c r="E2">
-        <v>32</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -606,10 +606,10 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D3">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E3">
         <v>29</v>
@@ -668,22 +668,22 @@
         <v>9</v>
       </c>
       <c r="C2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D2">
         <v>1</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F2">
         <v>26</v>
       </c>
       <c r="G2">
-        <v>78.79000000000001</v>
+        <v>76.47</v>
       </c>
       <c r="H2">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -694,10 +694,10 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3">
         <v>5</v>
@@ -706,7 +706,7 @@
         <v>24</v>
       </c>
       <c r="G3">
-        <v>82.76000000000001</v>
+        <v>80</v>
       </c>
       <c r="H3">
         <v>7.1</v>

--- a/docentes/Gomez Lopez Javier - Estadisticos 20222.xlsx
+++ b/docentes/Gomez Lopez Javier - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="20">
   <si>
     <t>Mat</t>
   </si>
@@ -70,31 +70,13 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
     <t>TENTZOHUA</t>
   </si>
   <si>
-    <t>COMIHUA</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
     <t>LEÓN</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>MARIA TERESA</t>
-  </si>
-  <si>
     <t>RUBI</t>
-  </si>
-  <si>
-    <t>ALEJANDRO GABRIEL</t>
   </si>
 </sst>
 </file>
@@ -719,7 +701,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -751,16 +733,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920260</v>
+        <v>21330051920107</v>
       </c>
       <c r="B2" t="s">
         <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -769,52 +751,6 @@
         <v>9</v>
       </c>
       <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>21330051920107</v>
-      </c>
-      <c r="B3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>21330051920036</v>
-      </c>
-      <c r="B4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4">
         <v>2</v>
       </c>
     </row>

--- a/docentes/Gomez Lopez Javier - Estadisticos 20222.xlsx
+++ b/docentes/Gomez Lopez Javier - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="23">
   <si>
     <t>Mat</t>
   </si>
@@ -70,13 +70,22 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>TENTZOHUA</t>
-  </si>
-  <si>
-    <t>LEÓN</t>
-  </si>
-  <si>
-    <t>RUBI</t>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>ESTRADA</t>
+  </si>
+  <si>
+    <t>FATIMA</t>
+  </si>
+  <si>
+    <t>GIOVANI</t>
   </si>
 </sst>
 </file>
@@ -477,16 +486,16 @@
         <v>34</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>7</v>
       </c>
       <c r="F2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G2">
-        <v>76.47</v>
+        <v>79.41</v>
       </c>
       <c r="H2">
         <v>7.1</v>
@@ -503,16 +512,16 @@
         <v>30</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>5</v>
       </c>
       <c r="F3">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G3">
-        <v>80</v>
+        <v>83.33</v>
       </c>
       <c r="H3">
         <v>7.1</v>
@@ -568,16 +577,19 @@
         <v>34</v>
       </c>
       <c r="D2">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>79.41</v>
+      </c>
+      <c r="H2">
+        <v>7.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -591,16 +603,19 @@
         <v>30</v>
       </c>
       <c r="D3">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>80</v>
+      </c>
+      <c r="H3">
+        <v>7.3</v>
       </c>
     </row>
   </sheetData>
@@ -653,19 +668,19 @@
         <v>34</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>7</v>
       </c>
       <c r="F2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G2">
-        <v>76.47</v>
+        <v>79.41</v>
       </c>
       <c r="H2">
-        <v>7.1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -679,10 +694,10 @@
         <v>30</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F3">
         <v>24</v>
@@ -691,7 +706,7 @@
         <v>80</v>
       </c>
       <c r="H3">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
     </row>
   </sheetData>
@@ -701,7 +716,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -733,16 +748,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920107</v>
+        <v>21330051920086</v>
       </c>
       <c r="B2" t="s">
         <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -752,6 +767,29 @@
       </c>
       <c r="G2">
         <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>21330051920041</v>
+      </c>
+      <c r="B3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Gomez Lopez Javier - Estadisticos 20222.xlsx
+++ b/docentes/Gomez Lopez Javier - Estadisticos 20222.xlsx
@@ -789,7 +789,7 @@
         <v>10</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Gomez Lopez Javier - Estadisticos 20222.xlsx
+++ b/docentes/Gomez Lopez Javier - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="29">
   <si>
     <t>Mat</t>
   </si>
@@ -73,19 +73,37 @@
     <t>MARTINEZ</t>
   </si>
   <si>
+    <t>TENTZOHUA</t>
+  </si>
+  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
     <t>RIVERA</t>
   </si>
   <si>
+    <t>LEÓN</t>
+  </si>
+  <si>
     <t>ESTRADA</t>
   </si>
   <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
     <t>FATIMA</t>
   </si>
   <si>
+    <t>RUBI</t>
+  </si>
+  <si>
     <t>GIOVANI</t>
+  </si>
+  <si>
+    <t>MARIA TERESA</t>
   </si>
 </sst>
 </file>
@@ -680,7 +698,7 @@
         <v>79.41</v>
       </c>
       <c r="H2">
-        <v>7</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -697,16 +715,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G3">
-        <v>80</v>
+        <v>83.33</v>
       </c>
       <c r="H3">
-        <v>7.4</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -716,7 +734,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -754,10 +772,10 @@
         <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -771,25 +789,71 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920041</v>
+        <v>21330051920107</v>
       </c>
       <c r="B3" t="s">
         <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D3" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G3">
         <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>21330051920041</v>
+      </c>
+      <c r="B4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>21330051920260</v>
+      </c>
+      <c r="B5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Gomez Lopez Javier - Estadisticos 20222.xlsx
+++ b/docentes/Gomez Lopez Javier - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="26">
   <si>
     <t>Mat</t>
   </si>
@@ -76,9 +76,6 @@
     <t>TENTZOHUA</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
@@ -88,9 +85,6 @@
     <t>LEÓN</t>
   </si>
   <si>
-    <t>ESTRADA</t>
-  </si>
-  <si>
     <t>CAMPOS</t>
   </si>
   <si>
@@ -98,9 +92,6 @@
   </si>
   <si>
     <t>RUBI</t>
-  </si>
-  <si>
-    <t>GIOVANI</t>
   </si>
   <si>
     <t>MARIA TERESA</t>
@@ -734,7 +725,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -772,10 +763,10 @@
         <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -795,10 +786,10 @@
         <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -812,47 +803,24 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920041</v>
+        <v>21330051920260</v>
       </c>
       <c r="B4" t="s">
         <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>21330051920260</v>
-      </c>
-      <c r="B5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" t="s">
-        <v>28</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G5">
         <v>1</v>
       </c>
     </row>
